--- a/results/04_bray_curtis_NMDS/artifacts/04_updated_data.xlsx
+++ b/results/04_bray_curtis_NMDS/artifacts/04_updated_data.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.47593396521867</v>
+        <v>-1.263805910646341</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3016179211792979</v>
+        <v>-0.0595803891092151</v>
       </c>
       <c r="D5" t="n">
-        <v>0.47298940588143</v>
+        <v>0.4757298129740735</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1129063915327732</v>
+        <v>0.3773242942189526</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6770172972950964</v>
+        <v>0.6016867684477103</v>
       </c>
       <c r="D6" t="n">
-        <v>0.558849267045555</v>
+        <v>0.5086780821298952</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2102408482021045</v>
+        <v>0.000321079422200214</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1024305678806738</v>
+        <v>0.2476799363155154</v>
       </c>
       <c r="D7" t="n">
-        <v>0.478389343227313</v>
+        <v>0.4819131155002738</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,17 +578,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8541215353797987</v>
+        <v>-1.319079349322728</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1602473788173033</v>
+        <v>-0.08978953087707928</v>
       </c>
       <c r="D8" t="n">
-        <v>3.150259813071328</v>
+        <v>0.4770873387638628</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.516427289150481</v>
+        <v>-1.301130188557845</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2822380444851039</v>
+        <v>-0.008976760098898411</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4742795103366564</v>
+        <v>0.4762744151171981</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04412306188067193</v>
+        <v>0.4978400068820437</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6936826641248622</v>
+        <v>0.5192203748667327</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5865887104208469</v>
+        <v>0.530430103903485</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.510428813103003</v>
+        <v>-1.263245848694662</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02077078711369859</v>
+        <v>-0.2066530415722991</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4733582612226925</v>
+        <v>0.475939541054659</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5229583347625468</v>
+        <v>0.1927793873097288</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6936852200799005</v>
+        <v>0.5868584642514852</v>
       </c>
       <c r="D12" t="n">
-        <v>8.032319269384283</v>
+        <v>0.5042977333737085</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03615735009330803</v>
+        <v>0.4432098650912106</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5963258125039714</v>
+        <v>0.4429527018990913</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5931380304586715</v>
+        <v>0.524418965180509</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08153191247718344</v>
+        <v>0.2980471575815188</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5213426111926217</v>
+        <v>0.450223409447607</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5365262345320553</v>
+        <v>0.5087687677990286</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -725,17 +725,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.168153146203305</v>
+        <v>-0.4321631120737372</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1576465257425665</v>
+        <v>0.08789166930003112</v>
       </c>
       <c r="D15" t="n">
-        <v>3.078549180888051</v>
+        <v>0.4322592521109467</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03566210437489201</v>
+        <v>-0.2515644108829654</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.008765364091568688</v>
+        <v>-0.112343490415391</v>
       </c>
       <c r="D16" t="n">
-        <v>1.511728154465206</v>
+        <v>0.4004822262034736</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01825329646755065</v>
+        <v>0.1285360868422665</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.08807631269251318</v>
+        <v>0.05352569661950742</v>
       </c>
       <c r="D17" t="n">
-        <v>0.459220907566171</v>
+        <v>0.473508724166799</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2387523000705463</v>
+        <v>0.3018416602527974</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6964523329504391</v>
+        <v>0.7041394626577248</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5564560727401155</v>
+        <v>0.5089318172287842</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.9016946384219313</v>
+        <v>-1.35750444895311</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04432530509044401</v>
+        <v>-0.008340031942792718</v>
       </c>
       <c r="D19" t="n">
-        <v>2.071926223607077</v>
+        <v>0.4743323010579151</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07703514049917001</v>
+        <v>0.3024373703908399</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4795411204346314</v>
+        <v>0.4357121590866621</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5674915116353485</v>
+        <v>0.5027494146835522</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.7271423252186239</v>
+        <v>-1.118893106248116</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1007688603551679</v>
+        <v>0.01515433719885972</v>
       </c>
       <c r="D21" t="n">
-        <v>2.586506695270131</v>
+        <v>0.4736672729581344</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.5719350664239553</v>
+        <v>-0.9290878302812425</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02640897797217947</v>
+        <v>-0.05198913964280951</v>
       </c>
       <c r="D22" t="n">
-        <v>1.881949036206343</v>
+        <v>0.4706445911994174</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.15865833471324</v>
+        <v>0.3728753139800448</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2662318301847753</v>
+        <v>0.1190925594056381</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6223415465541887</v>
+        <v>0.5463043037610378</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.9269972293231358</v>
+        <v>-1.411865775132268</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3181985287975967</v>
+        <v>0.1632419872457377</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.30889289604938</v>
+        <v>0.4784266106552182</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07234877693601499</v>
+        <v>0.3713645279958007</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3988419288461404</v>
+        <v>0.2807226520299222</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5973167337450264</v>
+        <v>0.5105294969744629</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -956,17 +956,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7132068723022136</v>
+        <v>-1.109622693655619</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.03329092411592841</v>
+        <v>-0.04381834073767862</v>
       </c>
       <c r="D26" t="n">
-        <v>1.334683103915436</v>
+        <v>0.4764843559893582</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8823333875720437</v>
+        <v>-1.323183149683737</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005222413720988263</v>
+        <v>-0.06160232892811103</v>
       </c>
       <c r="D27" t="n">
-        <v>1.661877780939228</v>
+        <v>0.4781438384153884</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.218147668277141</v>
+        <v>-1.041660177484122</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4579690051505105</v>
+        <v>-0.25005311527151</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4757612417081648</v>
+        <v>0.4799029899620638</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1019,17 +1019,17 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.8942986572069405</v>
+        <v>-1.333025565015429</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02591496870592426</v>
+        <v>-0.04008753990402863</v>
       </c>
       <c r="D29" t="n">
-        <v>1.899635002406852</v>
+        <v>0.4765252880787864</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1061,17 +1061,17 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6493531625139949</v>
+        <v>0.4180881954009089</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1217642317348659</v>
+        <v>0.1472302995997558</v>
       </c>
       <c r="D31" t="n">
-        <v>2.687204896938144</v>
+        <v>0.5224001452622388</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7690104569999771</v>
+        <v>0.5418195964777369</v>
       </c>
       <c r="C34" t="n">
-        <v>0.631158745688392</v>
+        <v>0.647652045138295</v>
       </c>
       <c r="D34" t="n">
-        <v>7.431891514087582</v>
+        <v>0.5217496112874516</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1145,17 +1145,17 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9567239492739907</v>
+        <v>-1.422422192684155</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1822158858012608</v>
+        <v>-0.2218954913109087</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03803569981369453</v>
+        <v>0.4802164329903011</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1187,17 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9543721111753999</v>
+        <v>-1.419478891485356</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2468837035112253</v>
+        <v>-0.2650103508283819</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6415886504504433</v>
+        <v>0.4777781449713894</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3273700307357196</v>
+        <v>0.3978555884086835</v>
       </c>
       <c r="C38" t="n">
-        <v>0.07792351325112128</v>
+        <v>-0.1073894800762522</v>
       </c>
       <c r="D38" t="n">
-        <v>0.521133656481659</v>
+        <v>0.5301332675852419</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6411330974955484</v>
+        <v>0.346018542865097</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3811965283284611</v>
+        <v>-0.602286744981456</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4841725254713246</v>
+        <v>0.5165281287904997</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1250,17 +1250,17 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9531037637190823</v>
+        <v>-1.413667639990328</v>
       </c>
       <c r="C40" t="n">
-        <v>0.05838408600850111</v>
+        <v>-0.04718589228783586</v>
       </c>
       <c r="D40" t="n">
-        <v>2.206658816569602</v>
+        <v>0.4837201220904856</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1271,17 +1271,17 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3795113346444854</v>
+        <v>-0.160405932962756</v>
       </c>
       <c r="C41" t="n">
-        <v>0.561431700900928</v>
+        <v>0.312405731850729</v>
       </c>
       <c r="D41" t="n">
-        <v>6.808234154512357</v>
+        <v>0.4759544605572718</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1334,17 +1334,17 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.05824108421670762</v>
+        <v>-0.3207620025204777</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.36591962156575</v>
+        <v>-0.5517695271456636</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.814244964841166</v>
+        <v>0.4595483164235006</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2533090465543629</v>
+        <v>-0.2658341065338233</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.7213960188505322</v>
+        <v>-0.5774978026377076</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4248412404607379</v>
+        <v>0.4587081762444715</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1376,17 +1376,17 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.9928074231817055</v>
+        <v>-1.478062319745293</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07982024393821524</v>
+        <v>-0.0747563042866084</v>
       </c>
       <c r="D46" t="n">
-        <v>2.409417273556593</v>
+        <v>0.4780076087945736</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.75671305088152</v>
+        <v>-1.50159766452218</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.5242736025343659</v>
+        <v>-0.1343632389456459</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4797554428636827</v>
+        <v>0.4834904557487863</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1559892618422583</v>
+        <v>0.1679731782522422</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3035827524941573</v>
+        <v>0.3157834287378842</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6021468636902286</v>
+        <v>0.5286610915456477</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.671660663751827</v>
+        <v>-1.474825386408682</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.5503684148967323</v>
+        <v>-0.1545393352924003</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4797550698677838</v>
+        <v>0.483490126239028</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.065757265631704</v>
+        <v>-0.4804504834522446</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1828262661658229</v>
+        <v>0.9469681903808941</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4850628560382415</v>
+        <v>0.4851480566937493</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2129195218423713</v>
+        <v>0.4707296651769401</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9893645217360575</v>
+        <v>0.8929090491235394</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5590140814133451</v>
+        <v>0.5119632876526844</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1454110754401516</v>
+        <v>0.2990780435078337</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1154345807142595</v>
+        <v>0.04362309497642097</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4981960547834865</v>
+        <v>0.4967431509760017</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1544,17 +1544,17 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7569282449824732</v>
+        <v>0.487852240711627</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1876517630413365</v>
+        <v>0.2648322633175371</v>
       </c>
       <c r="D54" t="n">
-        <v>3.294535733896975</v>
+        <v>0.5338833536656165</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.9144357895751055</v>
+        <v>-0.6418632291035772</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4833324969853628</v>
+        <v>0.7468518997509246</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4879010079003148</v>
+        <v>0.5126368967971273</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2833057286585406</v>
+        <v>0.2784844199161922</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.06112782518608273</v>
+        <v>-0.1739691295831163</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3930775552168806</v>
+        <v>0.4728275305017359</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.08187264378323386</v>
+        <v>0.4498152613414079</v>
       </c>
       <c r="C58" t="n">
-        <v>0.792024423318031</v>
+        <v>0.6677018828650311</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5711681604210247</v>
+        <v>0.5144687250306411</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7448907056297086</v>
+        <v>0.3543867572466682</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5010296387713117</v>
+        <v>-0.7483611774017197</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4656512377540214</v>
+        <v>0.4925241556658744</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1691,17 +1691,17 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.05824108421670759</v>
+        <v>-0.3207620025204776</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.36591962156575</v>
+        <v>-0.5517695271456637</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.814244964841166</v>
+        <v>0.4595483164235006</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1733,17 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4397679093765359</v>
+        <v>-0.1059735591984358</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4018764292812587</v>
+        <v>-0.09617063227151013</v>
       </c>
       <c r="D63" t="n">
-        <v>5.315318403482447</v>
+        <v>0.4848701401931964</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5107581544364271</v>
+        <v>0.2647788511157652</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4158549050119399</v>
+        <v>-0.5465801137059182</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4286402817963101</v>
+        <v>0.4644753958747067</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1775,17 +1775,17 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5662733689993834</v>
+        <v>0.3315387786089951</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5484417761097471</v>
+        <v>-0.6673367770067912</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.560481096572203</v>
+        <v>0.4918758332356116</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1796,17 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5641398730605038</v>
+        <v>0.3384648396557219</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5867762510691453</v>
+        <v>-0.7172922187801514</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.918017637383826</v>
+        <v>0.4917884145403321</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3566954969240967</v>
+        <v>0.423201039538875</v>
       </c>
       <c r="C67" t="n">
-        <v>0.09392873985283251</v>
+        <v>-0.1061534553031481</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4662009711966756</v>
+        <v>0.5044077407184578</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.09198298540012255</v>
+        <v>0.2983563977614094</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4666023975324193</v>
+        <v>0.4243109723060909</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5566289035679242</v>
+        <v>0.4827718974634529</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1859,17 +1859,17 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4307096661083222</v>
+        <v>-0.7785958617804062</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1328477191635534</v>
+        <v>-0.009549417246489429</v>
       </c>
       <c r="D69" t="n">
-        <v>2.865320133956799</v>
+        <v>0.4664089317816339</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1689534760025343</v>
+        <v>0.2580553457056431</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.01410398676978117</v>
+        <v>-0.0550070849481782</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3862829509262936</v>
+        <v>0.4810758392788047</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.1553565316925562</v>
+        <v>0.3711309705470999</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7407031228898323</v>
+        <v>0.6804138845182918</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5530874931568283</v>
+        <v>0.5063186682162552</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1377793054204409</v>
+        <v>0.4942921014031912</v>
       </c>
       <c r="C72" t="n">
-        <v>0.530792355391597</v>
+        <v>0.3204853712995602</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6075491063717906</v>
+        <v>0.5309679450096898</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4239758282055555</v>
+        <v>0.2878125868556401</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2498960240831857</v>
+        <v>-0.3747667963872137</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4200257210214308</v>
+        <v>0.4658267218327315</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.1779821775077516</v>
+        <v>0.08718063274828264</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1193927818810826</v>
+        <v>0.2531759067025279</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4820304216552235</v>
+        <v>0.5253105364463058</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.377720675678226</v>
+        <v>-1.187875800605224</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2468866772263636</v>
+        <v>0.02293588334232368</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4694316067791539</v>
+        <v>0.4715505277881247</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.2406653820401296</v>
+        <v>0.3805904205735733</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8668375308470537</v>
+        <v>0.8094534739751768</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5628647713326171</v>
+        <v>0.5065195849161103</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.2021930281692808</v>
+        <v>0.3640537028650209</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1747159747831859</v>
+        <v>0.03970230133036735</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5449004135616755</v>
+        <v>0.4895775910075226</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.748198248859907</v>
+        <v>-1.468057681471746</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.3968786544573278</v>
+        <v>-0.05778482140958115</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4760142529230728</v>
+        <v>0.4780076087945736</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3572433227128988</v>
+        <v>0.367768041804167</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.05560888282075255</v>
+        <v>-0.1954468576225064</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4537064715529134</v>
+        <v>0.5173221442896179</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.01036939577013751</v>
+        <v>0.3084714605279009</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3914764238669438</v>
+        <v>0.322132410520347</v>
       </c>
       <c r="D81" t="n">
-        <v>0.5729380777910438</v>
+        <v>0.4840641380899509</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.259560077389406</v>
+        <v>0.4386681177239589</v>
       </c>
       <c r="C82" t="n">
-        <v>1.000896714694173</v>
+        <v>0.9187941640526295</v>
       </c>
       <c r="D82" t="n">
-        <v>0.556401839370681</v>
+        <v>0.5121424227774598</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.1013113205491972</v>
+        <v>0.5350908892086597</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7143152894381447</v>
+        <v>0.5101710329617555</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5761809345003722</v>
+        <v>0.5239162836494401</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3531165869818981</v>
+        <v>0.2284858873473393</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.3106666994200905</v>
+        <v>-0.3693379165952054</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4068623554248265</v>
+        <v>0.4582894597051841</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5391612256925371</v>
+        <v>0.3483237599914027</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.2458431615194262</v>
+        <v>-0.4474559089135073</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4454171173202057</v>
+        <v>0.4892938818105954</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6021899648140072</v>
+        <v>0.357378709975721</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.304056688113409</v>
+        <v>-0.5276628302172242</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4571496061667639</v>
+        <v>0.4906830958746917</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.3877602867745604</v>
+        <v>-0.3554256017800433</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.7781136329619649</v>
+        <v>0.6602693224195838</v>
       </c>
       <c r="D87" t="n">
-        <v>0.485265172010407</v>
+        <v>0.4867820330690221</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.04054070352098461</v>
+        <v>0.5871537144704396</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.4989022043081982</v>
+        <v>-0.2622978154605823</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4579290471977245</v>
+        <v>0.47586337575027</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2279,17 +2279,17 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.9526251293843989</v>
+        <v>-1.424428479506747</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1270206051992412</v>
+        <v>-0.1688384587329237</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4766865441782864</v>
+        <v>0.4780947198791789</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.2748553120349969</v>
+        <v>0.0529176827869834</v>
       </c>
       <c r="C90" t="n">
-        <v>0.248164321688719</v>
+        <v>0.3878969777794127</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5115999943862053</v>
+        <v>0.4904460789482143</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.1857407709539315</v>
+        <v>-0.09142786896757639</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.3350312910256146</v>
+        <v>0.1104329380051958</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4763698896896135</v>
+        <v>0.4767214139017432</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1276418371364895</v>
+        <v>0.2948261531437616</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1233260917837897</v>
+        <v>0.06230362836639255</v>
       </c>
       <c r="D92" t="n">
-        <v>0.5025654371487476</v>
+        <v>0.4834896867392069</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.09115269308805671</v>
+        <v>0.1980791615205077</v>
       </c>
       <c r="C93" t="n">
-        <v>0.265657705872221</v>
+        <v>0.282207949511912</v>
       </c>
       <c r="D93" t="n">
-        <v>0.5687872479646079</v>
+        <v>0.4959380093285299</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4860135662007407</v>
+        <v>-0.3642927694053077</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.3490607595782542</v>
+        <v>0.3002285273248199</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4645209504200495</v>
+        <v>0.4788411276196098</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.07601426365322193</v>
+        <v>0.1342967922192206</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1848402533535628</v>
+        <v>-0.08674147673528347</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4181585309727485</v>
+        <v>0.4826469684611231</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2426,17 +2426,17 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5348492330895885</v>
+        <v>0.2947029586635806</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.6476351143993136</v>
+        <v>-0.7653942788482323</v>
       </c>
       <c r="D96" t="n">
-        <v>-4.483842250602508</v>
+        <v>0.4950165430216789</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2447,17 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.585194219837159</v>
+        <v>0.3543867572466039</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.6088828177725102</v>
+        <v>-0.748361177401739</v>
       </c>
       <c r="D97" t="n">
-        <v>-4.12574159079979</v>
+        <v>0.4925241556658744</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.01299303742997787</v>
+        <v>0.4230457759190041</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5886782407603522</v>
+        <v>0.4445577809071055</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5922999708163029</v>
+        <v>0.5259095593014289</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7307818180938455</v>
+        <v>0.3500095645797634</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.4943050389597306</v>
+        <v>-0.735650866055389</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4652071108302833</v>
+        <v>0.4924278875513218</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2510,17 +2510,17 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5851942206169788</v>
+        <v>0.3543867572466036</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.6088828171879307</v>
+        <v>-0.7483611774017391</v>
       </c>
       <c r="D100" t="n">
-        <v>-4.12574158539924</v>
+        <v>0.4925241556658744</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5509656225669078</v>
+        <v>0.3075933963999646</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.3651400202062509</v>
+        <v>-0.5416666657396483</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4588569185660586</v>
+        <v>0.4915275836571402</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2573,17 +2573,17 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.3490319568044397</v>
+        <v>-0.08527554764421322</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7806619496015283</v>
+        <v>0.6620201071269888</v>
       </c>
       <c r="D103" t="n">
-        <v>8.855894484602572</v>
+        <v>0.4868936061219153</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.6033562305425764</v>
+        <v>-0.2661380264540212</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.7233101456214258</v>
+        <v>0.9222514866293804</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4873756308168612</v>
+        <v>0.4892154759412653</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2615,17 +2615,17 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5941042087887706</v>
+        <v>0.3439597402320656</v>
       </c>
       <c r="C105" t="n">
-        <v>0.07583754389584811</v>
+        <v>0.08251422653149502</v>
       </c>
       <c r="D105" t="n">
-        <v>2.262501948155736</v>
+        <v>0.4831922455871839</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.376471877213984</v>
+        <v>0.1594702187108285</v>
       </c>
       <c r="C106" t="n">
-        <v>0.5222179623190203</v>
+        <v>0.6585292241785187</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5541015962522844</v>
+        <v>0.5015685791873464</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-1.597379642922403</v>
+        <v>-1.388803284833371</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.3981338945212309</v>
+        <v>-0.05925798008769737</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4753744393536596</v>
+        <v>0.4773707972407304</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.4178335394139593</v>
+        <v>-0.3029763280768361</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.02476908184108622</v>
+        <v>0.03251885532924972</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4456021043553223</v>
+        <v>0.4431882473973542</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.03015919717267611</v>
+        <v>0.06133610192417472</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2095806063006356</v>
+        <v>-0.01914971279977107</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4331975811224157</v>
+        <v>0.4551481156176905</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6264549378313375</v>
+        <v>0.3171957987342446</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.4365350242323157</v>
+        <v>-0.6335014680657506</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4593234143656185</v>
+        <v>0.486869629747419</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.7547874830250272</v>
+        <v>-0.5536747703877538</v>
       </c>
       <c r="C111" t="n">
-        <v>0.08035955499546807</v>
+        <v>0.2944062866032546</v>
       </c>
       <c r="D111" t="n">
-        <v>0.433598001254045</v>
+        <v>0.436268505980315</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2762,13 +2762,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.14660711192436</v>
+        <v>0.2937656933860541</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5665932340987591</v>
+        <v>0.5475492484691906</v>
       </c>
       <c r="D112" t="n">
-        <v>0.5600309243051665</v>
+        <v>0.5070346089290549</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.4456529766969419</v>
+        <v>0.1753579396014351</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6860734248119416</v>
+        <v>0.8277242740960638</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5498883684526824</v>
+        <v>0.5074021738060197</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.2267689129416534</v>
+        <v>0.1971023235376856</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.2109046604744494</v>
+        <v>-0.2132823791272341</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4106855424924082</v>
+        <v>0.4619658397624457</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.4546102194316837</v>
+        <v>-0.3028703502178344</v>
       </c>
       <c r="C115" t="n">
-        <v>0.01488152988703314</v>
+        <v>0.1450642768233686</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4182593719050945</v>
+        <v>0.4212663788737858</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.05304571240973761</v>
+        <v>-0.1739841470497063</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.7201151225020727</v>
+        <v>-0.4489617044412851</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4745798554645034</v>
+        <v>0.4839646226227518</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1034695480395475</v>
+        <v>0.1250935032291021</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.2084331113173336</v>
+        <v>-0.134463932187408</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3850206317554953</v>
+        <v>0.4435623442039596</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2888,13 +2888,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3287990880440005</v>
+        <v>0.2367776410778156</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.2502094810458835</v>
+        <v>-0.3125540190298876</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4149436902889437</v>
+        <v>0.4614161880003543</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6601557862032091</v>
+        <v>0.327060331170372</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.4683618145689457</v>
+        <v>-0.6716765688357678</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4631547660349578</v>
+        <v>0.489647188356299</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.26473886798227</v>
+        <v>0.107728804805042</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.4935856445825118</v>
+        <v>-0.4482587723992852</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4385809837285355</v>
+        <v>0.4735757358325284</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4341046776699816</v>
+        <v>0.2770471583729033</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.2104387830968674</v>
+        <v>-0.3672304052721932</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4403907587510826</v>
+        <v>0.4751226033674111</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5686137868734956</v>
+        <v>0.3054178746599258</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.403625322952499</v>
+        <v>-0.5725150514145829</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4471056397028776</v>
+        <v>0.4763589538276123</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5292802703790863</v>
+        <v>0.2663190074711499</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.4604525985464663</v>
+        <v>-0.5882835913382628</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4405560922753865</v>
+        <v>0.4744068309147584</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.239741608398535</v>
+        <v>-0.2546256862723202</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.6234502900870241</v>
+        <v>0.3124347945723613</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4809850145062841</v>
+        <v>0.4828695361527274</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.08239674382998781</v>
+        <v>-0.05395966740384777</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.6199846999733611</v>
+        <v>-0.4480448570543083</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4345915918410781</v>
+        <v>0.4672940495568431</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6576740120544906</v>
+        <v>0.325688483905665</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.4726193748046749</v>
+        <v>-0.6725415072325636</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4569419670227697</v>
+        <v>0.4832598961526038</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3868094191609721</v>
+        <v>0.1848714558740996</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.4659744940872876</v>
+        <v>-0.5084479605086616</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4421886984927725</v>
+        <v>0.4765447504836521</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6659094416634292</v>
+        <v>0.3418754891290785</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.4065937379772407</v>
+        <v>-0.6355798388884645</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4603369096534147</v>
+        <v>0.4912217334337615</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.3257913647533927</v>
+        <v>-0.3973113030633071</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.8887902654628724</v>
+        <v>0.6769547197200683</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4886432858216304</v>
+        <v>0.4900173967573474</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6456283964879945</v>
+        <v>0.3234265336843622</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.4502360335959288</v>
+        <v>-0.6526433777648526</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4633357306923986</v>
+        <v>0.4911378157657359</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6517118109930131</v>
+        <v>0.3299340221551444</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.4333524411315323</v>
+        <v>-0.6462494574020368</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4620018793500779</v>
+        <v>0.4917334245328341</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3224,13 +3224,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3155478762318286</v>
+        <v>0.3483392169511907</v>
       </c>
       <c r="C134" t="n">
-        <v>0.01342007249326826</v>
+        <v>-0.1355603080604019</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4233257741523353</v>
+        <v>0.5045098781216824</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5733647793960813</v>
+        <v>0.3283121350354601</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.3271572389120846</v>
+        <v>-0.5255873645147194</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4660288272363493</v>
+        <v>0.5038897522736846</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3695028352079739</v>
+        <v>0.3087195174269814</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.1233493282038098</v>
+        <v>-0.2529412901454802</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4340429050123378</v>
+        <v>0.489846295672887</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3329,17 +3329,17 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2487931909031906</v>
+        <v>-0.2022259334461066</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4762521098526265</v>
+        <v>0.1901571685600363</v>
       </c>
       <c r="D139" t="n">
-        <v>6.022497225469675</v>
+        <v>0.4853963913961802</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.08045478882156687</v>
+        <v>-0.1043982367205121</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.4846198174083351</v>
+        <v>-0.3772254738565726</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4251721041039673</v>
+        <v>0.4839251781632136</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5889291390683002</v>
+        <v>0.3168880551547384</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.3868421785253181</v>
+        <v>-0.5735412316644243</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4559030364561314</v>
+        <v>0.4850837445550102</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-0.3941325926327208</v>
+        <v>-0.03768353118697778</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4068153142686757</v>
+        <v>0.4828470528018847</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5290808227638661</v>
+        <v>0.4770468295917754</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3413,17 +3413,17 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5601159078368882</v>
+        <v>0.2423124007173281</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1006837460843312</v>
+        <v>-0.1860024847515756</v>
       </c>
       <c r="D143" t="n">
-        <v>0.6178010516540853</v>
+        <v>0.4531530310359551</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4407365268745133</v>
+        <v>-0.02794038976137231</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3452584062542326</v>
+        <v>-0.01620223853579819</v>
       </c>
       <c r="D145" t="n">
-        <v>4.786970627353033</v>
+        <v>0.473147639371674</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -3476,17 +3476,17 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5515776810198733</v>
+        <v>0.3282648361379564</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.4864529224848865</v>
+        <v>-0.6108722548568926</v>
       </c>
       <c r="D146" t="n">
-        <v>-2.981070791596402</v>
+        <v>0.5048374295355711</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-0.6134009350582228</v>
+        <v>0.006635588969870647</v>
       </c>
       <c r="C147" t="n">
-        <v>0.580848241192473</v>
+        <v>0.8100321047350355</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5414079674756478</v>
+        <v>0.5387891403259135</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3518,17 +3518,17 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5462953495587931</v>
+        <v>0.2773483642046677</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.1907076230896134</v>
+        <v>-0.2388923347351782</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.2212209223681595</v>
+        <v>0.4478326433306265</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.1912167627566002</v>
+        <v>0.392578649714363</v>
       </c>
       <c r="C149" t="n">
-        <v>0.2500360846349712</v>
+        <v>0.09591326462083481</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5938099041024306</v>
+        <v>0.5164505286604285</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.2966853109965183</v>
+        <v>0.4105335713144916</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1376889726161592</v>
+        <v>-0.04494424252548186</v>
       </c>
       <c r="D150" t="n">
-        <v>0.5696854483302243</v>
+        <v>0.5484940344959124</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.2620980441033311</v>
+        <v>0.1462327016613527</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.3835689247255694</v>
+        <v>-0.3598459328667988</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4332182090632548</v>
+        <v>0.4727473039056032</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-1.456777662619126</v>
+        <v>-1.256582439161977</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.2849006789049388</v>
+        <v>-0.005286263651344557</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4753152697907218</v>
+        <v>0.4798516420888095</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-0.6943430708291234</v>
+        <v>-0.6895961146715219</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.270849421823297</v>
+        <v>1.134635437417843</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4908378976091619</v>
+        <v>0.4936766091480937</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3917931833727932</v>
+        <v>0.3745275629265639</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.03659531165806065</v>
+        <v>-0.2214529681759164</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4383258583252636</v>
+        <v>0.5076087477148378</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-0.07471228568473202</v>
+        <v>0.3538476591671192</v>
       </c>
       <c r="C157" t="n">
-        <v>0.599606232790843</v>
+        <v>0.5229336724412672</v>
       </c>
       <c r="D157" t="n">
-        <v>0.5868453557903268</v>
+        <v>0.5235071168426271</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3728,13 +3728,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-0.142343519741457</v>
+        <v>0.4493117395653134</v>
       </c>
       <c r="C158" t="n">
-        <v>0.843827263643816</v>
+        <v>0.7411030174552862</v>
       </c>
       <c r="D158" t="n">
-        <v>0.574293130517545</v>
+        <v>0.5255978737403298</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.07478124940916933</v>
+        <v>0.4186497354696779</v>
       </c>
       <c r="C159" t="n">
-        <v>0.4913284364484694</v>
+        <v>0.3427756990645537</v>
       </c>
       <c r="D159" t="n">
-        <v>0.6153944530047205</v>
+        <v>0.5351526445897067</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.2295093854400592</v>
+        <v>0.379010612251773</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1775369551633513</v>
+        <v>0.01809480113327403</v>
       </c>
       <c r="D161" t="n">
-        <v>0.5959792221804416</v>
+        <v>0.5631359653849927</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.06514471349758609</v>
+        <v>0.1853613430367514</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.109408599537293</v>
+        <v>-0.04573849947756551</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4410399912076317</v>
+        <v>0.4702731187436164</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.4955075856279838</v>
+        <v>0.1975919060678452</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.1346887550296496</v>
+        <v>-0.368444943446833</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4831971106450846</v>
+        <v>0.5574263980401361</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-0.231756574135576</v>
+        <v>0.5361478806308558</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4738230430231171</v>
+        <v>0.4036531819366718</v>
       </c>
       <c r="D165" t="n">
-        <v>0.6180642413064653</v>
+        <v>0.5753977136694821</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.1384183937796352</v>
+        <v>0.4536979196521428</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4446316942476511</v>
+        <v>0.2591859532990313</v>
       </c>
       <c r="D166" t="n">
-        <v>0.6292972939248205</v>
+        <v>0.5370982370763382</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.3303415002647231</v>
+        <v>0.3908536618955887</v>
       </c>
       <c r="C167" t="n">
-        <v>0.06695129986548791</v>
+        <v>-0.1133760235134046</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4958227242895565</v>
+        <v>0.5387676892096316</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-0.0416937037176959</v>
+        <v>0.3342030877994436</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4845259318799387</v>
+        <v>0.4109330783625973</v>
       </c>
       <c r="D168" t="n">
-        <v>0.5637221665935043</v>
+        <v>0.5053494600534767</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.3035858031312325</v>
+        <v>0.4119635048878386</v>
       </c>
       <c r="C169" t="n">
-        <v>0.131496300130459</v>
+        <v>-0.0540254674916185</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5715855831417866</v>
+        <v>0.5340455206981706</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.3639555390510053</v>
+        <v>0.4259119668915345</v>
       </c>
       <c r="C170" t="n">
-        <v>0.08967828906442758</v>
+        <v>-0.1173206297892146</v>
       </c>
       <c r="D170" t="n">
-        <v>0.5479107048819</v>
+        <v>0.5673974300436475</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5297452305632405</v>
+        <v>0.3404798247606853</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.2544485618207754</v>
+        <v>-0.4469695388035746</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4572592657909142</v>
+        <v>0.495041930569822</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4022,13 +4022,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.3682621043877207</v>
+        <v>0.315534714161122</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.07978342034256483</v>
+        <v>-0.24150747244832</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4383082680881215</v>
+        <v>0.5025227208134836</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4043,17 +4043,17 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-0.1394612986973294</v>
+        <v>-0.4733068226518828</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1832697064966658</v>
+        <v>0.06400169934509567</v>
       </c>
       <c r="D173" t="n">
-        <v>3.315644738094781</v>
+        <v>0.5094167813593121</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.5587225788958111</v>
+        <v>0.3553503268041787</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.251161749201689</v>
+        <v>-0.4616308166021111</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4588433062833312</v>
+        <v>0.495704730491098</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.1351197235304516</v>
+        <v>0.4944259682978698</v>
       </c>
       <c r="C175" t="n">
-        <v>0.5359124980815206</v>
+        <v>0.3252775123234736</v>
       </c>
       <c r="D175" t="n">
-        <v>0.606483635069291</v>
+        <v>0.5307064081233748</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0246866591123726</v>
+        <v>0.4410147697983697</v>
       </c>
       <c r="C176" t="n">
-        <v>0.602795871038499</v>
+        <v>0.4540015902217183</v>
       </c>
       <c r="D176" t="n">
-        <v>0.6124635368659853</v>
+        <v>0.5430920680279614</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.1560995358031962</v>
+        <v>0.4646343903416056</v>
       </c>
       <c r="C177" t="n">
-        <v>0.4398836519730649</v>
+        <v>0.2467027146276899</v>
       </c>
       <c r="D177" t="n">
-        <v>0.6483418539558016</v>
+        <v>0.55135868245022</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.08220616425128212</v>
+        <v>0.3783989560764126</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3926667342410438</v>
+        <v>0.2648464585779511</v>
       </c>
       <c r="D178" t="n">
-        <v>0.6206753268956083</v>
+        <v>0.5120360693928819</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.2475819911348505</v>
+        <v>0.3982402491688997</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4726813496822444</v>
+        <v>0.2580512725070002</v>
       </c>
       <c r="D179" t="n">
-        <v>0.5829125889663602</v>
+        <v>0.5421158552812133</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -4190,13 +4190,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.5958525687115502</v>
+        <v>0.4628105448134219</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.03254593882045789</v>
+        <v>-0.3145426486288246</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4747138111562261</v>
+        <v>0.522333448689011</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -4211,17 +4211,17 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.5636755056668215</v>
+        <v>0.311851883938237</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.1867909346960394</v>
+        <v>-0.2013433727053054</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.185877873886914</v>
+        <v>0.4853578663672139</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.07666824893785118</v>
+        <v>0.4234566581882061</v>
       </c>
       <c r="C182" t="n">
-        <v>0.476145128672617</v>
+        <v>0.321685095542586</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6435879928854814</v>
+        <v>0.5469661324299359</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.2052624447752839</v>
+        <v>0.4107813042488335</v>
       </c>
       <c r="C183" t="n">
-        <v>0.2632794261366344</v>
+        <v>0.09566473713799975</v>
       </c>
       <c r="D183" t="n">
-        <v>0.6196136093982847</v>
+        <v>0.5274187618204162</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4274,17 +4274,17 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.5593363767887226</v>
+        <v>0.3037988981134373</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.06148101379863005</v>
+        <v>-0.07743931759123815</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9836404357288836</v>
+        <v>0.5342907157410183</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.2105906975626978</v>
+        <v>0.4106808178715026</v>
       </c>
       <c r="C185" t="n">
-        <v>0.2560337474929669</v>
+        <v>0.0869385588699409</v>
       </c>
       <c r="D185" t="n">
-        <v>0.617508372473061</v>
+        <v>0.5373590075651997</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4316,13 +4316,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-0.04305910326878392</v>
+        <v>0.2535532665613673</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2656998481579907</v>
+        <v>0.2675512213390266</v>
       </c>
       <c r="D186" t="n">
-        <v>0.6709293694492442</v>
+        <v>0.566820790952717</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -4337,13 +4337,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-0.003356762716052549</v>
+        <v>0.4486272631803346</v>
       </c>
       <c r="C187" t="n">
-        <v>0.7376469835809458</v>
+        <v>0.5933585233418147</v>
       </c>
       <c r="D187" t="n">
-        <v>0.6048970779869498</v>
+        <v>0.5383886800097588</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.1268403098866511</v>
+        <v>0.3772158405123741</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3301178836778004</v>
+        <v>0.1853360027068864</v>
       </c>
       <c r="D188" t="n">
-        <v>0.6529280034142567</v>
+        <v>0.5276629420545798</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4379,17 +4379,17 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.5970846375905956</v>
+        <v>0.3786946417697061</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.3314721612188551</v>
+        <v>-0.3732441929644794</v>
       </c>
       <c r="D189" t="n">
-        <v>-1.538152858493388</v>
+        <v>0.4917436337855094</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.05291277110729312</v>
+        <v>0.1021643922493363</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.2234702570940667</v>
+        <v>-0.09281934939453319</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4459100122948514</v>
+        <v>0.4967644305843976</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.04279127947496639</v>
+        <v>0.4342317852581726</v>
       </c>
       <c r="C191" t="n">
-        <v>0.5951984395556823</v>
+        <v>0.4449091556613253</v>
       </c>
       <c r="D191" t="n">
-        <v>0.6442755174230917</v>
+        <v>0.5673655666327057</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.7784389294251641</v>
+        <v>-0.2188715908359614</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4880418297694881</v>
+        <v>0.5397603024948314</v>
       </c>
       <c r="D192" t="n">
-        <v>0.5010020312856527</v>
+        <v>0.503434994360519</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4463,17 +4463,17 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-0.1344176928772546</v>
+        <v>-0.4098181087043496</v>
       </c>
       <c r="C193" t="n">
-        <v>0.04483611874355113</v>
+        <v>-0.008858796478588067</v>
       </c>
       <c r="D193" t="n">
-        <v>2.023625866645307</v>
+        <v>0.4447398110916018</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.3038049855256836</v>
+        <v>-0.09892422736548984</v>
       </c>
       <c r="C194" t="n">
-        <v>-1.05146696323333</v>
+        <v>-0.9834518907737958</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5189291072385293</v>
+        <v>0.5193962445195021</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4505,17 +4505,17 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-0.2172114458212024</v>
+        <v>-0.549738879794837</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.236478253217026</v>
+        <v>-0.3584820396369476</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.5954830874806573</v>
+        <v>0.4914289864031112</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4526,13 +4526,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-0.4586002262691427</v>
+        <v>-0.3578626431280567</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.2641761058040861</v>
+        <v>0.07516482597186198</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4502968512726966</v>
+        <v>0.462100157317734</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.6791130111933263</v>
+        <v>-0.5754798321339267</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.2067021958989024</v>
+        <v>-0.05450223218921812</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4686620866418176</v>
+        <v>0.4744826791091341</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.4819581648628627</v>
+        <v>0.3356276893726291</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.2059727187223898</v>
+        <v>-0.3814586932271984</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4469149052372659</v>
+        <v>0.4920806357121664</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4589,17 +4589,17 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.3126281793309191</v>
+        <v>-0.6238123032116789</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.02410540193817622</v>
+        <v>-0.1549435686468272</v>
       </c>
       <c r="D199" t="n">
-        <v>1.392684740753298</v>
+        <v>0.4614199614943988</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4610,17 +4610,17 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.3204130166442796</v>
+        <v>0.006683285657536788</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.2546770525487296</v>
+        <v>-0.4023564564116714</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.8024723063171704</v>
+        <v>0.4452655985125332</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-0.377928156944303</v>
+        <v>-0.3528400451397823</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.424375394397988</v>
+        <v>-0.008390928215738008</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4404099742714896</v>
+        <v>0.4509943420987606</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -4652,17 +4652,17 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.3385639337423688</v>
+        <v>-0.1379826734217726</v>
       </c>
       <c r="C202" t="n">
-        <v>0.397531929182252</v>
+        <v>0.01374037677785224</v>
       </c>
       <c r="D202" t="n">
-        <v>5.281781049809779</v>
+        <v>0.4875839762805802</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4673,17 +4673,17 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.1695796285125971</v>
+        <v>-0.8054306540610097</v>
       </c>
       <c r="C203" t="n">
-        <v>0.9352157240980654</v>
+        <v>0.7624975751010996</v>
       </c>
       <c r="D203" t="n">
-        <v>10.33384404882573</v>
+        <v>0.4730447013803303</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-0.1090975236678319</v>
+        <v>-0.1803894205934219</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.625644552963786</v>
+        <v>-0.2509681389131809</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4849755508559713</v>
+        <v>0.4896431809313289</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -4736,13 +4736,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.5850695003339543</v>
+        <v>0.3589979090209581</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.277764855435137</v>
+        <v>-0.496033139997098</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4641092088927645</v>
+        <v>0.4993395145269293</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-0.84383659939955</v>
+        <v>-0.7268661006071583</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.3171125119595832</v>
+        <v>0.1458950448672131</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4589714357350076</v>
+        <v>0.4686519920042961</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4625414144322917</v>
+        <v>0.3532546429402699</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.05776282221343467</v>
+        <v>-0.2587648810473849</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4787934358224329</v>
+        <v>0.536545968073703</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.4601330691212771</v>
+        <v>0.3852131225211708</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.09077323701274763</v>
+        <v>-0.2974827635877378</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4490800783897562</v>
+        <v>0.5052636313806809</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-0.003192737932591353</v>
+        <v>0.09744050406913303</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.01033484698913085</v>
+        <v>0.003662938412620655</v>
       </c>
       <c r="D210" t="n">
-        <v>0.3946569766027663</v>
+        <v>0.4527683312205939</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-0.1415108987080894</v>
+        <v>0.2199182316522198</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4222245056415845</v>
+        <v>0.4203308834278571</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5546999815604245</v>
+        <v>0.5029661810284141</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4862,17 +4862,17 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0.1633493365808723</v>
+        <v>-0.4588279765737702</v>
       </c>
       <c r="C212" t="n">
-        <v>0.04964079892858413</v>
+        <v>-0.05658769273277248</v>
       </c>
       <c r="D212" t="n">
-        <v>2.0704574475813</v>
+        <v>0.451551839950058</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -4883,13 +4883,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-0.2089020423352695</v>
+        <v>0.02556256486689361</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1172437518432575</v>
+        <v>0.2344020533024273</v>
       </c>
       <c r="D213" t="n">
-        <v>0.441938928731035</v>
+        <v>0.5080687575091122</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-0.5063011436897766</v>
+        <v>-0.1924709191550942</v>
       </c>
       <c r="C214" t="n">
-        <v>0.1096907539201461</v>
+        <v>0.419228712170345</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4741233598197043</v>
+        <v>0.4983254398683405</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.02382916641777098</v>
+        <v>0.3339364551501935</v>
       </c>
       <c r="C215" t="n">
-        <v>0.3905710267378117</v>
+        <v>0.3120264945006955</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5881101201333588</v>
+        <v>0.5097173291140633</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -4946,13 +4946,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.426542712124888</v>
+        <v>0.3561981120316621</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.1035280620402653</v>
+        <v>-0.2915292807557265</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4460443146121164</v>
+        <v>0.4954941426118807</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -4967,13 +4967,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.227508867786438</v>
+        <v>0.1608075198089795</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.2973233176951501</v>
+        <v>-0.2722963097886292</v>
       </c>
       <c r="D217" t="n">
-        <v>0.424435404879946</v>
+        <v>0.4735403455877102</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-0.008558617090054179</v>
+        <v>0.3196450972074603</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4164687169682865</v>
+        <v>0.3520120412458081</v>
       </c>
       <c r="D218" t="n">
-        <v>0.6008039806299443</v>
+        <v>0.5228136655400302</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5009,13 +5009,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.2486788346211577</v>
+        <v>0.2226482467716101</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.1786767259231283</v>
+        <v>-0.2178457679068901</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4069396969755156</v>
+        <v>0.4631600688472832</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.3571332320128115</v>
+        <v>0.2628392633448317</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.2212170710120924</v>
+        <v>-0.311373329002173</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4233008375067809</v>
+        <v>0.4721220352015791</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5114,17 +5114,17 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.5479503529824676</v>
+        <v>0.3146810304597119</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.3627072148495434</v>
+        <v>-0.4392078898488707</v>
       </c>
       <c r="D224" t="n">
-        <v>-1.826196778154819</v>
+        <v>0.4918878385737215</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.3224691227755455</v>
+        <v>0.4362314028925517</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1576555079383018</v>
+        <v>-0.04576767601407358</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5586710577032185</v>
+        <v>0.5420456759109358</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.216543302885199</v>
+        <v>0.2525028201811143</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.08371194673273688</v>
+        <v>-0.1304300127991196</v>
       </c>
       <c r="D228" t="n">
-        <v>0.3888856763006785</v>
+        <v>0.455892895435649</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -5240,13 +5240,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.1928657883529509</v>
+        <v>0.3217918672949518</v>
       </c>
       <c r="C230" t="n">
-        <v>0.1024321919449456</v>
+        <v>0.003562449282106554</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4948416608582761</v>
+        <v>0.4969882498959875</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.4630287057875979</v>
+        <v>0.2505922964784792</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.3513972739109206</v>
+        <v>-0.4713849721375077</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4564156088843877</v>
+        <v>0.4988690601519287</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.4467819259879955</v>
+        <v>0.216176934908762</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.4801309804084469</v>
+        <v>-0.5531267925205738</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4407493484908603</v>
+        <v>0.4744882152611895</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-0.1535010196692484</v>
+        <v>0.5001511817981315</v>
       </c>
       <c r="C234" t="n">
-        <v>0.9886625837615527</v>
+        <v>0.8654481340942978</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5874099970722405</v>
+        <v>0.5406519560059617</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.1212857825903381</v>
+        <v>0.3433550734960776</v>
       </c>
       <c r="C235" t="n">
-        <v>0.2418174268387759</v>
+        <v>0.1364948056226678</v>
       </c>
       <c r="D235" t="n">
-        <v>0.6307881169212742</v>
+        <v>0.5144801188728054</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5366,17 +5366,17 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.7676253046878929</v>
+        <v>0.5524013814131469</v>
       </c>
       <c r="C236" t="n">
-        <v>0.3894602437410725</v>
+        <v>0.4532271818730187</v>
       </c>
       <c r="D236" t="n">
-        <v>5.176792459807408</v>
+        <v>0.55575862365632</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Centroid-Proj</t>
+          <t>BC-Direct</t>
         </is>
       </c>
     </row>
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.4213087092966041</v>
+        <v>0.2976096153345051</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.2262013794280384</v>
+        <v>-0.3552199619401533</v>
       </c>
       <c r="D237" t="n">
-        <v>0.4111388184344312</v>
+        <v>0.460157423208647</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>

--- a/results/04_bray_curtis_NMDS/artifacts/04_updated_data.xlsx
+++ b/results/04_bray_curtis_NMDS/artifacts/04_updated_data.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.263805910646341</v>
+        <v>0.4100931347131228</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0595803891092151</v>
+        <v>0.06172261764210434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4757298129740735</v>
+        <v>0.8211686076025618</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3773242942189526</v>
+        <v>0.7729802852999409</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6016867684477103</v>
+        <v>0.007708224011052523</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5086780821298952</v>
+        <v>0.5521975237134342</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000321079422200214</v>
+        <v>0.1729568682043588</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2476799363155154</v>
+        <v>0.4450671111772715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4819131155002738</v>
+        <v>0.5444127170219605</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -578,13 +578,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.319079349322728</v>
+        <v>-0.07277700647999354</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08978953087707928</v>
+        <v>-1.514849431822976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4770873387638628</v>
+        <v>0.502688712054063</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.301130188557845</v>
+        <v>-0.244669993384102</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.008976760098898411</v>
+        <v>1.480900835462279</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4762744151171981</v>
+        <v>0.5084315073709802</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4978400068820437</v>
+        <v>0.720482838815745</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5192203748667327</v>
+        <v>-0.140203062472364</v>
       </c>
       <c r="D10" t="n">
-        <v>0.530430103903485</v>
+        <v>0.5395899975333966</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.263245848694662</v>
+        <v>0.4294756199442885</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2066530415722991</v>
+        <v>0.394264364798617</v>
       </c>
       <c r="D11" t="n">
-        <v>0.475939541054659</v>
+        <v>0.655319574750813</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1927793873097288</v>
+        <v>0.6597334698097945</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5868584642514852</v>
+        <v>0.2866103006072611</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5042977333737085</v>
+        <v>0.5666400383379567</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4432098650912106</v>
+        <v>0.6111025505791294</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4429527018990913</v>
+        <v>-0.1052538764734907</v>
       </c>
       <c r="D13" t="n">
-        <v>0.524418965180509</v>
+        <v>0.5528802097314044</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2980471575815188</v>
+        <v>0.5871699250856901</v>
       </c>
       <c r="C14" t="n">
-        <v>0.450223409447607</v>
+        <v>-0.02422947469343866</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5087687677990286</v>
+        <v>0.5507054724891783</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4321631120737372</v>
+        <v>0.3014009431916686</v>
       </c>
       <c r="C15" t="n">
-        <v>0.08789166930003112</v>
+        <v>0.5422209534690375</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4322592521109467</v>
+        <v>0.5451306435063576</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2515644108829654</v>
+        <v>-0.07499737830922416</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.112343490415391</v>
+        <v>-0.4447177449565175</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4004822262034736</v>
+        <v>0.4819160790004194</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1285360868422665</v>
+        <v>0.02356752363008941</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05352569661950742</v>
+        <v>0.2796109719780917</v>
       </c>
       <c r="D17" t="n">
-        <v>0.473508724166799</v>
+        <v>0.5032155085885248</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3018416602527974</v>
+        <v>0.8345080839991108</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7041394626577248</v>
+        <v>0.1602075828601788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5089318172287842</v>
+        <v>0.5520404238149552</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.35750444895311</v>
+        <v>0.5003596369336651</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.008340031942792718</v>
+        <v>-0.07866772982522972</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4743323010579151</v>
+        <v>0.8867175724877209</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3024373703908399</v>
+        <v>0.5551277301928572</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4357121590866621</v>
+        <v>0.04693379772073398</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5027494146835522</v>
+        <v>0.5847387322223798</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.118893106248116</v>
+        <v>0.3387312953039927</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01515433719885972</v>
+        <v>-0.1113857576349982</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4736672729581344</v>
+        <v>0.9072482039435299</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.9290878302812425</v>
+        <v>0.2033815794958355</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.05198913964280951</v>
+        <v>-0.0278422042748769</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4706445911994174</v>
+        <v>0.7835862612343321</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3728753139800448</v>
+        <v>0.1863814622123004</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1190925594056381</v>
+        <v>-0.1164768605989578</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5463043037610378</v>
+        <v>0.4601330684084095</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.411865775132268</v>
+        <v>0.04522449244995295</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1632419872457377</v>
+        <v>-1.553736488831803</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4784266106552182</v>
+        <v>0.5089951191359313</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3713645279958007</v>
+        <v>0.3799628693333321</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2807226520299222</v>
+        <v>-0.04224195855498145</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5105294969744629</v>
+        <v>0.5612150335754945</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.109622693655619</v>
+        <v>0.2654002929336577</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.04381834073767862</v>
+        <v>0.07260272347285948</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4764843559893582</v>
+        <v>0.7799225991733564</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.323183149683737</v>
+        <v>0.4721815572208149</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.06160232892811103</v>
+        <v>-0.07450255282403258</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4781438384153884</v>
+        <v>0.8972305375616331</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.041660177484122</v>
+        <v>0.2564122646929127</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.25005311527151</v>
+        <v>-0.2899633280428975</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4799029899620638</v>
+        <v>0.8392944031428415</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.333025565015429</v>
+        <v>0.4733340062206522</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.04008753990402863</v>
+        <v>-0.0886114677389009</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4765252880787864</v>
+        <v>0.9112129432393474</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8906109454363538</v>
+        <v>0.4370576020027541</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4719018035345383</v>
+        <v>-0.004256526249863805</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6071669668171503</v>
+        <v>0.840141315080297</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4180881954009089</v>
+        <v>0.2331874589695889</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1472302995997558</v>
+        <v>-0.1438394797001616</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5224001452622388</v>
+        <v>0.4673372428585147</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.060016723118041</v>
+        <v>0.4731430022407981</v>
       </c>
       <c r="C32" t="n">
-        <v>0.413619710020885</v>
+        <v>0.5537045739539537</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5705167756828456</v>
+        <v>0.6187993325695919</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6051804358412021</v>
+        <v>0.2646209929794046</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4760590123444854</v>
+        <v>-0.04419370335896393</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5757888602173612</v>
+        <v>0.8256225991441355</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5418195964777369</v>
+        <v>0.8826738067258854</v>
       </c>
       <c r="C34" t="n">
-        <v>0.647652045138295</v>
+        <v>-0.140961532499947</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5217496112874516</v>
+        <v>0.527061686633154</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.422422192684155</v>
+        <v>0.5502397884524876</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2218954913109087</v>
+        <v>0.2235730087306762</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4802164329903011</v>
+        <v>0.7149399483611741</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3942927972267711</v>
+        <v>-0.4560193115993287</v>
       </c>
       <c r="C36" t="n">
-        <v>0.11019728058848</v>
+        <v>-0.1402768809561969</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2360322359398776</v>
+        <v>0.3336230289726209</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.419478891485356</v>
+        <v>0.5331454763353003</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2650103508283819</v>
+        <v>0.3189794490509971</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4777781449713894</v>
+        <v>0.6908422396057223</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3978555884086835</v>
+        <v>-0.09864154684287038</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1073894800762522</v>
+        <v>-0.1153571572466488</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5301332675852419</v>
+        <v>0.3396536062976906</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.346018542865097</v>
+        <v>-0.7003060525931877</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.602286744981456</v>
+        <v>-0.1710560334968626</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5165281287904997</v>
+        <v>0.4057067874646068</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.413667639990328</v>
+        <v>0.5265621047893472</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.04718589228783586</v>
+        <v>-0.1794692690766218</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4837201220904856</v>
+        <v>0.9296927209247681</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.160405932962756</v>
+        <v>-1.233336333083347</v>
       </c>
       <c r="C41" t="n">
-        <v>0.312405731850729</v>
+        <v>0.3937837990604982</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4759544605572718</v>
+        <v>0.3999593098724655</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.01355836878585115</v>
+        <v>-0.3931623661263239</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4071784110055495</v>
+        <v>-0.2046495724893655</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3934041906691045</v>
+        <v>0.3291913818582603</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.6564661110454164</v>
+        <v>-0.8685301957226234</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4230081792965504</v>
+        <v>-0.1471152176179847</v>
       </c>
       <c r="D43" t="n">
-        <v>0.05643717767358343</v>
+        <v>0.4006158463232914</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3207620025204777</v>
+        <v>-0.825877065479639</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.5517695271456636</v>
+        <v>0.1696108937159777</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4595483164235006</v>
+        <v>0.3930742517035495</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.2658341065338233</v>
+        <v>-0.4663573970219438</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.5774978026377076</v>
+        <v>-0.3043043688256694</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4587081762444715</v>
+        <v>0.2666298776334447</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.478062319745293</v>
+        <v>0.5523239244119343</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0747563042866084</v>
+        <v>-0.226113125224653</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4780076087945736</v>
+        <v>0.9020126335746079</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.50159766452218</v>
+        <v>0.5652383669641299</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1343632389456459</v>
+        <v>-0.3429027423796691</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4834904557487863</v>
+        <v>0.8319835043018808</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1679731782522422</v>
+        <v>0.3699138967247731</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3157834287378842</v>
+        <v>-0.2841400118486972</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5286610915456477</v>
+        <v>0.5701924469941322</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.474825386408682</v>
+        <v>0.55112364205314</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1545393352924003</v>
+        <v>-0.3532037138130263</v>
       </c>
       <c r="D49" t="n">
-        <v>0.483490126239028</v>
+        <v>0.8319950634650781</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.120467054308199</v>
+        <v>1.080698823635546</v>
       </c>
       <c r="C50" t="n">
-        <v>-1.050716931162444</v>
+        <v>-0.2670825650375329</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5416385445769418</v>
+        <v>0.5414551651322644</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4804504834522446</v>
+        <v>0.526420009965293</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9469681903808941</v>
+        <v>1.180227304870718</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4851480566937493</v>
+        <v>0.5399533153209415</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4707296651769401</v>
+        <v>1.092197073341646</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8929090491235394</v>
+        <v>-0.0926441048911545</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5119632876526844</v>
+        <v>0.5419152039261059</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2990780435078337</v>
+        <v>0.06651923531752681</v>
       </c>
       <c r="C53" t="n">
-        <v>0.04362309497642097</v>
+        <v>0.0235299911525159</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4967431509760017</v>
+        <v>0.4644488288292458</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.487852240711627</v>
+        <v>0.406102544350606</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2648322633175371</v>
+        <v>-0.1522423029221144</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5338833536656165</v>
+        <v>0.5243351625009574</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.6418632291035772</v>
+        <v>0.5607777372951832</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7468518997509246</v>
+        <v>-1.106830781304668</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5126368967971273</v>
+        <v>0.5337741188444168</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2784844199161922</v>
+        <v>-0.187049061742398</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1739691295831163</v>
+        <v>-0.1315125644411369</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4728275305017359</v>
+        <v>0.2883412873376571</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4078911815625323</v>
+        <v>0.2120806466689508</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6616647524667004</v>
+        <v>-0.2768704577503621</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5259700854188555</v>
+        <v>0.8104610106569508</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4498152613414079</v>
+        <v>0.8693334916337135</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6677018828650311</v>
+        <v>-0.07426698727980674</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5144687250306411</v>
+        <v>0.5369057158266815</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3543867572466682</v>
+        <v>-0.868530195722623</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.7483611774017197</v>
+        <v>-0.1471152176179854</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4925241556658744</v>
+        <v>0.4006158463232914</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1605072090433493</v>
+        <v>-0.2237094157345932</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.005762065924084731</v>
+        <v>0.08381145473519611</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4229862118456497</v>
+        <v>0.3890067955020879</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3207620025204776</v>
+        <v>-0.8258770654796351</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5517695271456637</v>
+        <v>0.1696108937159876</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4595483164235006</v>
+        <v>0.3930742517035495</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6296183123617812</v>
+        <v>-0.8435846447934531</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4097962788924349</v>
+        <v>-0.1401374732462092</v>
       </c>
       <c r="D62" t="n">
-        <v>0.04521810744595327</v>
+        <v>0.3995893007425158</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1059735591984358</v>
+        <v>-0.2174238832513473</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.09617063227151013</v>
+        <v>0.5770236954637046</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4848701401931964</v>
+        <v>0.5103425859516049</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.2647788511157652</v>
+        <v>-0.6500022775154541</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5465801137059182</v>
+        <v>-0.01992521788013302</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4644753958747067</v>
+        <v>0.3780325090502627</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3315387786089951</v>
+        <v>-0.7845335580690642</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.6673367770067912</v>
+        <v>-0.1128858634404117</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4918758332356116</v>
+        <v>0.3917839740646984</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3384648396557219</v>
+        <v>-0.834135705458796</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.7172922187801514</v>
+        <v>-0.1446045327882058</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4917884145403321</v>
+        <v>0.3981564861104439</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.423201039538875</v>
+        <v>-0.09638012591058751</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1061534553031481</v>
+        <v>-0.1514080105706407</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5044077407184578</v>
+        <v>0.3185230359749411</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2983563977614094</v>
+        <v>0.5483390558559293</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4243109723060909</v>
+        <v>-0.009457838626189157</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4827718974634529</v>
+        <v>0.5536371435331292</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1859,13 +1859,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7785958617804062</v>
+        <v>-0.003485384254273978</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.009549417246489429</v>
+        <v>-0.06417668102031247</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4664089317816339</v>
+        <v>0.6498561279009621</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.2580553457056431</v>
+        <v>-0.06176360308742785</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0550070849481782</v>
+        <v>0.07106478760397547</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4810758392788047</v>
+        <v>0.3646759581177945</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3711309705470999</v>
+        <v>0.8519157422257173</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6804138845182918</v>
+        <v>0.06114212297370329</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5063186682162552</v>
+        <v>0.56122128292078</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4942921014031912</v>
+        <v>0.4828530240166396</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3204853712995602</v>
+        <v>-0.1584070879358984</v>
       </c>
       <c r="D72" t="n">
-        <v>0.5309679450096898</v>
+        <v>0.5385482702253798</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.2878125868556401</v>
+        <v>-1.177894081815718</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3747667963872137</v>
+        <v>-0.3552666026054586</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4658267218327315</v>
+        <v>0.1645169710274335</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.08718063274828264</v>
+        <v>0.2904852584951023</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2531759067025279</v>
+        <v>0.2465922515757114</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5253105364463058</v>
+        <v>0.6414075692496191</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.187875800605224</v>
+        <v>0.3752074634332547</v>
       </c>
       <c r="C75" t="n">
-        <v>0.02293588334232368</v>
+        <v>-0.2016314314134354</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4715505277881247</v>
+        <v>0.8994716105686483</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.09939678000201774</v>
+        <v>0.8978335492542544</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8234241816285577</v>
+        <v>-0.1762783535220358</v>
       </c>
       <c r="D76" t="n">
-        <v>0.5352234199987503</v>
+        <v>0.5450679481715914</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3805904205735733</v>
+        <v>0.9931739289223771</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8094534739751768</v>
+        <v>-0.1098766274800678</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5065195849161103</v>
+        <v>0.5281579689861372</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3640537028650209</v>
+        <v>0.07994385945824264</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03970230133036735</v>
+        <v>-0.07040337194140672</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4895775910075226</v>
+        <v>0.388079717684997</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.468057681471746</v>
+        <v>0.5505715799975833</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.05778482140958115</v>
+        <v>-0.1462313501573664</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4780076087945736</v>
+        <v>0.9126050625872252</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.367768041804167</v>
+        <v>-0.2201992315301302</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1954468576225064</v>
+        <v>-0.1418450464049714</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5173221442896179</v>
+        <v>0.3490409839708287</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.3084714605279009</v>
+        <v>0.4276436576636382</v>
       </c>
       <c r="C81" t="n">
-        <v>0.322132410520347</v>
+        <v>-0.0274088903900651</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4840641380899509</v>
+        <v>0.5474179466033264</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4386681177239589</v>
+        <v>1.10201953382403</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9187941640526295</v>
+        <v>-0.1639590180435896</v>
       </c>
       <c r="D82" t="n">
-        <v>0.5121424227774598</v>
+        <v>0.5260652879244861</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5350908892086597</v>
+        <v>0.7163452966480529</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5101710329617555</v>
+        <v>-0.2036765177242128</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5239162836494401</v>
+        <v>0.5302644442073039</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.2284858873473393</v>
+        <v>-0.4405868590131552</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.3693379165952054</v>
+        <v>0.09319716886479237</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4582894597051841</v>
+        <v>0.3518139486584458</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.3483237599914027</v>
+        <v>-0.5314642654425422</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.4474559089135073</v>
+        <v>-0.1139193368688914</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4892938818105954</v>
+        <v>0.3610735073685815</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.357378709975721</v>
+        <v>-0.6248561359792649</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.5276628302172242</v>
+        <v>-0.1360559793547565</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4906830958746917</v>
+        <v>0.3754443757014539</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.3554256017800433</v>
+        <v>0.02972022130319084</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6602693224195838</v>
+        <v>1.038632573080617</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4867820330690221</v>
+        <v>0.5267723877114473</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5871537144704396</v>
+        <v>-0.3915456169675561</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.2622978154605823</v>
+        <v>0.4616331505160316</v>
       </c>
       <c r="D88" t="n">
-        <v>0.47586337575027</v>
+        <v>0.4881977263967693</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-1.424428479506747</v>
+        <v>-0.01603448912001789</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1688384587329237</v>
+        <v>-1.558599969940208</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4780947198791789</v>
+        <v>0.5081700715226456</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0529176827869834</v>
+        <v>0.4660804069609009</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3878969777794127</v>
+        <v>0.2303471948829249</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4904460789482143</v>
+        <v>0.5925940911798947</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.09142786896757639</v>
+        <v>-0.04033660974390538</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1104329380051958</v>
+        <v>0.5353449006334289</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4767214139017432</v>
+        <v>0.5564137641781275</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2948261531437616</v>
+        <v>0.08978706418481197</v>
       </c>
       <c r="C92" t="n">
-        <v>0.06230362836639255</v>
+        <v>0.03307874633516824</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4834896867392069</v>
+        <v>0.4785558879784997</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1980791615205077</v>
+        <v>0.3515779822787852</v>
       </c>
       <c r="C93" t="n">
-        <v>0.282207949511912</v>
+        <v>0.04624366393740565</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4959380093285299</v>
+        <v>0.5982127585515693</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.3642927694053077</v>
+        <v>0.1742084014222587</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3002285273248199</v>
+        <v>0.7569763146338563</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4788411276196098</v>
+        <v>0.5431682516072277</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.1342967922192206</v>
+        <v>-0.1272162927059989</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.08674147673528347</v>
+        <v>0.2414006925573138</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4826469684611231</v>
+        <v>0.4603714300350346</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2947029586635806</v>
+        <v>-0.8390849269183511</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.7653942788482323</v>
+        <v>-0.2656649676582534</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4950165430216789</v>
+        <v>0.4018473263991401</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3543867572466039</v>
+        <v>-0.8685301957226227</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.748361177401739</v>
+        <v>-0.1471152176179861</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4925241556658744</v>
+        <v>0.4006158463232914</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4230457759190041</v>
+        <v>0.6078828483488732</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4445577809071055</v>
+        <v>-0.128936701674552</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5259095593014289</v>
+        <v>0.539038634827128</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3500095645797634</v>
+        <v>-0.8545692812854059</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.735650866055389</v>
+        <v>-0.1388934676383356</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4924278875513218</v>
+        <v>0.3993066182226531</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.3543867572466036</v>
+        <v>-0.8685301957226228</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.7483611774017391</v>
+        <v>-0.147115217617985</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4925241556658744</v>
+        <v>0.4006158463232914</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.6564661110452126</v>
+        <v>-0.8685301957226215</v>
       </c>
       <c r="C101" t="n">
-        <v>0.423008179296802</v>
+        <v>-0.1471152176179886</v>
       </c>
       <c r="D101" t="n">
-        <v>0.05643717767358343</v>
+        <v>0.4006158463232914</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.3075933963999646</v>
+        <v>-0.6391836083612163</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.5416666657396483</v>
+        <v>-0.09245180652476513</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4915275836571402</v>
+        <v>0.3771275531447288</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.08527554764421322</v>
+        <v>0.5255508925510275</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6620201071269888</v>
+        <v>0.6870140428415462</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4868936061219153</v>
+        <v>0.5346094364427977</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.2661380264540212</v>
+        <v>0.4926500345486591</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9222514866293804</v>
+        <v>1.055976936348196</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4892154759412653</v>
+        <v>0.5259172496932386</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.3439597402320656</v>
+        <v>0.1333793861877716</v>
       </c>
       <c r="C105" t="n">
-        <v>0.08251422653149502</v>
+        <v>-0.06841885240448106</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4831922455871839</v>
+        <v>0.4259657693794635</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.1594702187108285</v>
+        <v>0.7282799415751692</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6585292241785187</v>
+        <v>0.3285710475583625</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5015685791873464</v>
+        <v>0.5701462925764725</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-1.388803284833371</v>
+        <v>0.5220677266045675</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.05925798008769737</v>
+        <v>-0.1829574702740615</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4773707972407304</v>
+        <v>0.9257465277263976</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.3029763280768361</v>
+        <v>0.1360117154590115</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03251885532924972</v>
+        <v>-0.5301491372194098</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4431882473973542</v>
+        <v>0.5242980801564321</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.06133610192417472</v>
+        <v>-0.07446992157044501</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.01914971279977107</v>
+        <v>0.3325220441089656</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4551481156176905</v>
+        <v>0.4695014254655143</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3171957987342446</v>
+        <v>-0.7469374820167456</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.6335014680657506</v>
+        <v>-0.09214291003071198</v>
       </c>
       <c r="D110" t="n">
-        <v>0.486869629747419</v>
+        <v>0.3890885842800074</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.5536747703877538</v>
+        <v>0.6548948158324797</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2944062866032546</v>
+        <v>0.5943037118305371</v>
       </c>
       <c r="D111" t="n">
-        <v>0.436268505980315</v>
+        <v>0.5621279694532416</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2762,13 +2762,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.2937656933860541</v>
+        <v>0.672813678350701</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5475492484691906</v>
+        <v>0.145550196799009</v>
       </c>
       <c r="D112" t="n">
-        <v>0.5070346089290549</v>
+        <v>0.5689515842025301</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1753579396014351</v>
+        <v>0.8782924994517965</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8277242740960638</v>
+        <v>0.3744872351936481</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5074021738060197</v>
+        <v>0.5589023579545079</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1971023235376856</v>
+        <v>-0.2647292246949169</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.2132823791272341</v>
+        <v>0.1451470528011894</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4619658397624457</v>
+        <v>0.3574289106907959</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.3028703502178344</v>
+        <v>0.2439302873403588</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1450642768233686</v>
+        <v>-0.4993558791617386</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4212663788737858</v>
+        <v>0.5459003752699015</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.1739841470497063</v>
+        <v>-0.4006723986697218</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.4489617044412851</v>
+        <v>0.6866737907038009</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4839646226227518</v>
+        <v>0.4940202005830877</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1250935032291021</v>
+        <v>-0.1751256890943708</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.134463932187408</v>
+        <v>0.2151826584982931</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4435623442039596</v>
+        <v>0.4187737557658058</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2888,13 +2888,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2367776410778156</v>
+        <v>-0.3808409424041485</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.3125540190298876</v>
+        <v>0.06801314653140793</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4614161880003543</v>
+        <v>0.3733983628600794</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.327060331170372</v>
+        <v>-0.7880746405693074</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.6716765688357678</v>
+        <v>-0.09659137870912018</v>
       </c>
       <c r="D119" t="n">
-        <v>0.489647188356299</v>
+        <v>0.3942986182225304</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.107728804805042</v>
+        <v>-0.515390298745743</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.4482587723992852</v>
+        <v>0.2917881207634379</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4735757358325284</v>
+        <v>0.4074863922443826</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2770471583729033</v>
+        <v>-0.4139223370116638</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.3672304052721932</v>
+        <v>-0.1169243791883468</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4751226033674111</v>
+        <v>0.3711592141177084</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.3054178746599258</v>
+        <v>-0.6801553005412758</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.5725150514145829</v>
+        <v>-0.06609282628526422</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4763589538276123</v>
+        <v>0.3767853074191685</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.2663190074711499</v>
+        <v>-0.6930136294277803</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5882835913382628</v>
+        <v>0.02220971944800629</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4744068309147584</v>
+        <v>0.4059037462597581</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.2546256862723202</v>
+        <v>-0.1386714670123457</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3124347945723613</v>
+        <v>0.7880132365904465</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4828695361527274</v>
+        <v>0.5302889558361632</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.05395966740384777</v>
+        <v>-0.4760489956766826</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.4480448570543083</v>
+        <v>0.5033692338391027</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4672940495568431</v>
+        <v>0.4383622093809417</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.325688483905665</v>
+        <v>-0.7903580646728326</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.6725415072325636</v>
+        <v>-0.08700979215737807</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4832598961526038</v>
+        <v>0.3904172113758876</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.1848714558740996</v>
+        <v>-0.5907680075962496</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.5084479605086616</v>
+        <v>0.1579201471701159</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4765447504836521</v>
+        <v>0.4106579685262904</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.6270138977828903</v>
+        <v>-0.7649873168804441</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3286665327719367</v>
+        <v>-0.06204156402181087</v>
       </c>
       <c r="D128" t="n">
-        <v>0.04460787492151308</v>
+        <v>0.3883590551923931</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.5967134710495772</v>
+        <v>-0.6564513231615381</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2631232717950343</v>
+        <v>0.0004976434098352118</v>
       </c>
       <c r="D129" t="n">
-        <v>0.09695147414038714</v>
+        <v>0.3933700809855107</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3418754891290785</v>
+        <v>-0.7446351344861144</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.6355798388884645</v>
+        <v>-0.1557388210558857</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4912217334337615</v>
+        <v>0.3909522992697106</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.3973113030633071</v>
+        <v>-0.1188095161231953</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6769547197200683</v>
+        <v>1.080660361892865</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4900173967573474</v>
+        <v>0.5255457968366729</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3234265336843622</v>
+        <v>-0.7665524202106987</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.6526433777648526</v>
+        <v>-0.1007409747209093</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4911378157657359</v>
+        <v>0.3913300933499523</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3299340221551444</v>
+        <v>-0.7585759159530229</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.6462494574020368</v>
+        <v>-0.1161112737077419</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4917334245328341</v>
+        <v>0.3898393200662869</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3224,13 +3224,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3483392169511907</v>
+        <v>-0.1383038756893784</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1355603080604019</v>
+        <v>-0.08971315999706678</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5045098781216824</v>
+        <v>0.2717873776870258</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3283121350354601</v>
+        <v>-0.6186135013613723</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.5255873645147194</v>
+        <v>-0.1229570997599705</v>
       </c>
       <c r="D135" t="n">
-        <v>0.5038897522736846</v>
+        <v>0.3709423661965863</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3087195174269814</v>
+        <v>-0.2823627685243233</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2529412901454802</v>
+        <v>-0.06878491865667302</v>
       </c>
       <c r="D136" t="n">
-        <v>0.489846295672887</v>
+        <v>0.3043635273331484</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-0.4737070837491584</v>
+        <v>0.1691103182349455</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.3151770985529492</v>
+        <v>0.1710989437253181</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4295967459232599</v>
+        <v>0.5702016907803787</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.656141782704274</v>
+        <v>-0.4178009906094447</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.3747399161641493</v>
+        <v>0.8760384958237479</v>
       </c>
       <c r="D138" t="n">
-        <v>0.7617586306191535</v>
+        <v>0.5001218095591954</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.2022259334461066</v>
+        <v>0.07461978119925899</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1901571685600363</v>
+        <v>-0.3921976269465522</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4853963913961802</v>
+        <v>0.5569604489493002</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.1043982367205121</v>
+        <v>-0.4096373506198037</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.3772254738565726</v>
+        <v>-0.3453671704072074</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4839251781632136</v>
+        <v>0.4575761742538312</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3168880551547384</v>
+        <v>-0.6814891216192139</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.5735412316644243</v>
+        <v>-0.08763024701440239</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4850837445550102</v>
+        <v>0.3789006715638836</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-0.03768353118697778</v>
+        <v>0.6790523846344211</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4828470528018847</v>
+        <v>0.1079903129617335</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4770468295917754</v>
+        <v>0.5867280101911888</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.2423124007173281</v>
+        <v>-0.2144575560987507</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1860024847515756</v>
+        <v>0.05214825638622227</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4531530310359551</v>
+        <v>0.3709880949095496</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3434,13 +3434,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.1726163759135955</v>
+        <v>0.2883531836327452</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.3470922581826883</v>
+        <v>-0.3212321399113877</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4905313589044499</v>
+        <v>0.6512046483859467</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.02794038976137231</v>
+        <v>-0.1300788110101193</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.01620223853579819</v>
+        <v>0.4764239530926645</v>
       </c>
       <c r="D145" t="n">
-        <v>0.473147639371674</v>
+        <v>0.4922047872444235</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3476,13 +3476,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3282648361379564</v>
+        <v>-0.7119553392864749</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.6108722548568926</v>
+        <v>-0.1367276661198557</v>
       </c>
       <c r="D146" t="n">
-        <v>0.5048374295355711</v>
+        <v>0.378315770264382</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.006635588969870647</v>
+        <v>0.7886408552058827</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8100321047350355</v>
+        <v>-0.587978639177349</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5387891403259135</v>
+        <v>0.565581672803353</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.2773483642046677</v>
+        <v>-0.2839687353924049</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.2388923347351782</v>
+        <v>0.008554026177706711</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4478326433306265</v>
+        <v>0.2907131842218198</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.392578649714363</v>
+        <v>0.1591811486613223</v>
       </c>
       <c r="C149" t="n">
-        <v>0.09591326462083481</v>
+        <v>-0.08606892112153525</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5164505286604285</v>
+        <v>0.4399746593883246</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4105335713144916</v>
+        <v>-0.01913760128083213</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.04494424252548186</v>
+        <v>-0.1351957673314416</v>
       </c>
       <c r="D150" t="n">
-        <v>0.5484940344959124</v>
+        <v>0.3542494397356024</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.1462327016613527</v>
+        <v>-0.4331664392087996</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.3598459328667988</v>
+        <v>0.2147243082420257</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4727473039056032</v>
+        <v>0.3946945789980533</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-1.256582439161977</v>
+        <v>0.09810923232873932</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.005286263651344557</v>
+        <v>-1.46194547904902</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4798516420888095</v>
+        <v>0.5220430238628068</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-0.6895961146715219</v>
+        <v>0.2176137147613086</v>
       </c>
       <c r="C153" t="n">
-        <v>1.134635437417843</v>
+        <v>1.472717293524157</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4936766091480937</v>
+        <v>0.5217871932584657</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3745275629265639</v>
+        <v>-0.252200476583144</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.2214529681759164</v>
+        <v>-0.1030918101474426</v>
       </c>
       <c r="D154" t="n">
-        <v>0.5076087477148378</v>
+        <v>0.313186762778276</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.3571768335587351</v>
+        <v>-0.6444490248440288</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.2017600914316225</v>
+        <v>0.6845282190708126</v>
       </c>
       <c r="D155" t="n">
-        <v>0.7968891574504354</v>
+        <v>0.4406308051323972</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3686,13 +3686,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-0.2916987268618902</v>
+        <v>0.7953959847865034</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.7259714333581814</v>
+        <v>-0.1398999087935159</v>
       </c>
       <c r="D156" t="n">
-        <v>0.5163229292442552</v>
+        <v>0.5414778216663602</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.3538476591671192</v>
+        <v>0.6777792252716862</v>
       </c>
       <c r="C157" t="n">
-        <v>0.5229336724412672</v>
+        <v>-0.02572568631533939</v>
       </c>
       <c r="D157" t="n">
-        <v>0.5235071168426271</v>
+        <v>0.5524120157706827</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3728,13 +3728,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.4493117395653134</v>
+        <v>0.9323253666750548</v>
       </c>
       <c r="C158" t="n">
-        <v>0.7411030174552862</v>
+        <v>-0.165166050903102</v>
       </c>
       <c r="D158" t="n">
-        <v>0.5255978737403298</v>
+        <v>0.5439667662241222</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.4186497354696779</v>
+        <v>0.4779328180758579</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3427756990645537</v>
+        <v>-0.118485527043371</v>
       </c>
       <c r="D159" t="n">
-        <v>0.5351526445897067</v>
+        <v>0.5468047715716708</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.4239142205527304</v>
+        <v>0.1739596893406388</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.02833887707173253</v>
+        <v>-0.9943428671764524</v>
       </c>
       <c r="D160" t="n">
-        <v>0.7509383828914674</v>
+        <v>0.535747998459062</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.379010612251773</v>
+        <v>0.06198738813253458</v>
       </c>
       <c r="C161" t="n">
-        <v>0.01809480113327403</v>
+        <v>-0.1327044608856824</v>
       </c>
       <c r="D161" t="n">
-        <v>0.5631359653849927</v>
+        <v>0.4023053989191825</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3812,13 +3812,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.8333594988217856</v>
+        <v>0.4846408726073291</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.3472533791054749</v>
+        <v>-1.348957177720902</v>
       </c>
       <c r="D162" t="n">
-        <v>0.7613827392060676</v>
+        <v>0.5190892505262706</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.1853613430367514</v>
+        <v>-0.06620811699301896</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.04573849947756551</v>
+        <v>0.1962408007558748</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4702731187436164</v>
+        <v>0.4729916247283245</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.1975919060678452</v>
+        <v>-0.3735734060086442</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.368444943446833</v>
+        <v>-0.2729003105800294</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5574263980401361</v>
+        <v>0.3668595713319309</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.5361478806308558</v>
+        <v>0.5473595516005771</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4036531819366718</v>
+        <v>-0.3747486030113856</v>
       </c>
       <c r="D165" t="n">
-        <v>0.5753977136694821</v>
+        <v>0.5910248283492263</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4536979196521428</v>
+        <v>0.3833790052030827</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2591859532990313</v>
+        <v>-0.1288761637972538</v>
       </c>
       <c r="D166" t="n">
-        <v>0.5370982370763382</v>
+        <v>0.5283659829902996</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.3908536618955887</v>
+        <v>-0.10397823463781</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.1133760235134046</v>
+        <v>-0.1338689256615288</v>
       </c>
       <c r="D167" t="n">
-        <v>0.5387676892096316</v>
+        <v>0.3409658678500068</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.3342030877994436</v>
+        <v>0.5347120400005483</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4109330783625973</v>
+        <v>-0.01080377859101407</v>
       </c>
       <c r="D168" t="n">
-        <v>0.5053494600534767</v>
+        <v>0.581427926046622</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3959,13 +3959,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.4119635048878386</v>
+        <v>-0.03265097578492365</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.0540254674916185</v>
+        <v>-0.1287881228262377</v>
       </c>
       <c r="D169" t="n">
-        <v>0.5340455206981706</v>
+        <v>0.3480054386686384</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.4259119668915345</v>
+        <v>-0.107254072974817</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.1173206297892146</v>
+        <v>-0.1605111917917854</v>
       </c>
       <c r="D170" t="n">
-        <v>0.5673974300436475</v>
+        <v>0.3550244614032229</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.3404798247606853</v>
+        <v>-0.5299802013837736</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.4469695388035746</v>
+        <v>-0.1105083583324364</v>
       </c>
       <c r="D171" t="n">
-        <v>0.495041930569822</v>
+        <v>0.3687555569656101</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4022,13 +4022,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.315534714161122</v>
+        <v>-0.2713204443754094</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.24150747244832</v>
+        <v>-0.1214341986094016</v>
       </c>
       <c r="D172" t="n">
-        <v>0.5025227208134836</v>
+        <v>0.306887822327998</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-0.4733068226518828</v>
+        <v>0.4019247220939928</v>
       </c>
       <c r="C173" t="n">
-        <v>0.06400169934509567</v>
+        <v>0.5482093818623798</v>
       </c>
       <c r="D173" t="n">
-        <v>0.5094167813593121</v>
+        <v>0.5293162257612239</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.3553503268041787</v>
+        <v>-0.5450798887427059</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.4616308166021111</v>
+        <v>-0.1346601033429498</v>
       </c>
       <c r="D174" t="n">
-        <v>0.495704730491098</v>
+        <v>0.3673359482378872</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.4944259682978698</v>
+        <v>0.4889920022206442</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3252775123234736</v>
+        <v>-0.1587322893089426</v>
       </c>
       <c r="D175" t="n">
-        <v>0.5307064081233748</v>
+        <v>0.5382222420157698</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.4410147697983697</v>
+        <v>0.6215927050676008</v>
       </c>
       <c r="C176" t="n">
-        <v>0.4540015902217183</v>
+        <v>-0.1390000794832574</v>
       </c>
       <c r="D176" t="n">
-        <v>0.5430920680279614</v>
+        <v>0.5611828943148965</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.4646343903416056</v>
+        <v>0.3701955425033202</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2467027146276899</v>
+        <v>-0.1580063120831023</v>
       </c>
       <c r="D177" t="n">
-        <v>0.55135868245022</v>
+        <v>0.555785753977891</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.3783989560764126</v>
+        <v>0.3654477963177665</v>
       </c>
       <c r="C178" t="n">
-        <v>0.2648464585779511</v>
+        <v>-0.07253294990533077</v>
       </c>
       <c r="D178" t="n">
-        <v>0.5120360693928819</v>
+        <v>0.5317029192871837</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.3982402491688997</v>
+        <v>0.3505938317603655</v>
       </c>
       <c r="C179" t="n">
-        <v>0.2580512725070002</v>
+        <v>-0.3529813944182674</v>
       </c>
       <c r="D179" t="n">
-        <v>0.5421158552812133</v>
+        <v>0.5708729530322225</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -4190,13 +4190,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.4628105448134219</v>
+        <v>-0.3491612039952167</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.3145426486288246</v>
+        <v>-0.3333018184614193</v>
       </c>
       <c r="D180" t="n">
-        <v>0.522333448689011</v>
+        <v>0.3494720586919788</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.311851883938237</v>
+        <v>-1.176602374432009</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.2013433727053054</v>
+        <v>-0.3656922604990135</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4853578663672139</v>
+        <v>0.2092781241754559</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.4234566581882061</v>
+        <v>0.4518713519490302</v>
       </c>
       <c r="C182" t="n">
-        <v>0.321685095542586</v>
+        <v>-0.1272439131357526</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5469661324299359</v>
+        <v>0.5564842435853311</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.4107813042488335</v>
+        <v>0.1630429954039971</v>
       </c>
       <c r="C183" t="n">
-        <v>0.09566473713799975</v>
+        <v>-0.1178725541485246</v>
       </c>
       <c r="D183" t="n">
-        <v>0.5274187618204162</v>
+        <v>0.4347527578835248</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3037988981134373</v>
+        <v>-1.164516797477696</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.07743931759123815</v>
+        <v>-0.1967812125605594</v>
       </c>
       <c r="D184" t="n">
-        <v>0.5342907157410183</v>
+        <v>0.2713012245594208</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.4106808178715026</v>
+        <v>0.1536032520973166</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0869385588699409</v>
+        <v>-0.1102623437618872</v>
       </c>
       <c r="D185" t="n">
-        <v>0.5373590075651997</v>
+        <v>0.4227389726936633</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4316,13 +4316,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.2535532665613673</v>
+        <v>0.3334959666757362</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2675512213390266</v>
+        <v>0.0744173429913081</v>
       </c>
       <c r="D186" t="n">
-        <v>0.566820790952717</v>
+        <v>0.6701076455213898</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -4337,13 +4337,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4486272631803346</v>
+        <v>0.7843110550161447</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5933585233418147</v>
+        <v>-0.1170829427772493</v>
       </c>
       <c r="D187" t="n">
-        <v>0.5383886800097588</v>
+        <v>0.5226945650153271</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3772158405123741</v>
+        <v>0.2711691985018838</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1853360027068864</v>
+        <v>-0.1077097995431944</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5276629420545798</v>
+        <v>0.5100830562496538</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.3786946417697061</v>
+        <v>-0.4432120782983151</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.3732441929644794</v>
+        <v>-0.1362098985497231</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4917436337855094</v>
+        <v>0.3413097743002591</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.1021643922493363</v>
+        <v>-0.1390929851545283</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.09281934939453319</v>
+        <v>0.2842035100811005</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4967644305843976</v>
+        <v>0.4718916188922844</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.4342317852581726</v>
+        <v>0.6081154929977584</v>
       </c>
       <c r="C191" t="n">
-        <v>0.4449091556613253</v>
+        <v>-0.1197637413107621</v>
       </c>
       <c r="D191" t="n">
-        <v>0.5673655666327057</v>
+        <v>0.5683965072250022</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-0.2188715908359614</v>
+        <v>0.05833199316443883</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5397603024948314</v>
+        <v>0.8427020362219384</v>
       </c>
       <c r="D192" t="n">
-        <v>0.503434994360519</v>
+        <v>0.5213132313870318</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-0.4098181087043496</v>
+        <v>0.17937804035208</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.008858796478588067</v>
+        <v>0.5188564511826229</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4447398110916018</v>
+        <v>0.5389992024968052</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-0.09892422736548984</v>
+        <v>-0.6372765438449031</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.9834518907737958</v>
+        <v>-0.9002430421371677</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5193962445195021</v>
+        <v>0.5129048248131346</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-0.549738879794837</v>
+        <v>-0.3577211748989221</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.3584820396369476</v>
+        <v>-0.7955902824560993</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4914289864031112</v>
+        <v>0.5062323156733964</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4526,13 +4526,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-0.3578626431280567</v>
+        <v>0.09770434025721417</v>
       </c>
       <c r="C196" t="n">
-        <v>0.07516482597186198</v>
+        <v>0.6367971956622266</v>
       </c>
       <c r="D196" t="n">
-        <v>0.462100157317734</v>
+        <v>0.5511670059801407</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.5754798321339267</v>
+        <v>0.03860135717968907</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.05450223218921812</v>
+        <v>-0.7767051886638474</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4744826791091341</v>
+        <v>0.5360836830994664</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.3356276893726291</v>
+        <v>-0.4549762283113134</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.3814586932271984</v>
+        <v>-0.08790621698251942</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4920806357121664</v>
+        <v>0.3424951751038985</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.6238123032116789</v>
+        <v>-0.3117143496440652</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.1549435686468272</v>
+        <v>0.8286932743732387</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4614199614943988</v>
+        <v>0.538106921675586</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.006683285657536788</v>
+        <v>-0.4959061710971755</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.4023564564116714</v>
+        <v>0.2278379646270769</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4452655985125332</v>
+        <v>0.395362944827621</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-0.3528400451397823</v>
+        <v>-0.07611263697769168</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.008390928215738008</v>
+        <v>0.6782626422326474</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4509943420987606</v>
+        <v>0.5390545844651139</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -4652,13 +4652,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.1379826734217726</v>
+        <v>-0.1293397457476064</v>
       </c>
       <c r="C202" t="n">
-        <v>0.01374037677785224</v>
+        <v>0.5686138058547896</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4875839762805802</v>
+        <v>0.5325769679040203</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -4673,13 +4673,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.8054306540610097</v>
+        <v>0.1799153275850884</v>
       </c>
       <c r="C203" t="n">
-        <v>0.7624975751010996</v>
+        <v>1.340172942406934</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4730447013803303</v>
+        <v>0.5290932538137388</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-0.1803894205934219</v>
+        <v>-0.2977328269104424</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.2509681389131809</v>
+        <v>0.6609258698013873</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4896431809313289</v>
+        <v>0.51376642246893</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-0.4577367396743269</v>
+        <v>-1.276493447424428</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.3318317814240419</v>
+        <v>-0.009028447376810118</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4278638522600708</v>
+        <v>0.3562534723972745</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4736,13 +4736,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3589979090209581</v>
+        <v>-0.5862236446924098</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.496033139997098</v>
+        <v>-0.1387685313303589</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4993395145269293</v>
+        <v>0.3720116863317548</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-0.7268661006071583</v>
+        <v>0.2739942132908982</v>
       </c>
       <c r="C207" t="n">
-        <v>0.1458950448672131</v>
+        <v>0.9997433693193511</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4686519920042961</v>
+        <v>0.5319402805029838</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3532546429402699</v>
+        <v>-0.2763868430264667</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.2587648810473849</v>
+        <v>-0.2476103623933035</v>
       </c>
       <c r="D208" t="n">
-        <v>0.536545968073703</v>
+        <v>0.3662511983463533</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.3852131225211708</v>
+        <v>-0.3413898467379091</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.2974827635877378</v>
+        <v>-0.1408677088584563</v>
       </c>
       <c r="D209" t="n">
-        <v>0.5052636313806809</v>
+        <v>0.3274985613143474</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.09744050406913303</v>
+        <v>0.01528770950091321</v>
       </c>
       <c r="C210" t="n">
-        <v>0.003662938412620655</v>
+        <v>0.04036643754149675</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4527683312205939</v>
+        <v>0.4450495115350676</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.2199182316522198</v>
+        <v>0.5320258968033232</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4203308834278571</v>
+        <v>0.06179110373140138</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5029661810284141</v>
+        <v>0.5910887387750403</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4862,13 +4862,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0.4588279765737702</v>
+        <v>0.03951104235684843</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.05658769273277248</v>
+        <v>0.6184846306042675</v>
       </c>
       <c r="D212" t="n">
-        <v>0.451551839950058</v>
+        <v>0.5397758901935155</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -4883,13 +4883,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.02556256486689361</v>
+        <v>0.2918785009295904</v>
       </c>
       <c r="C213" t="n">
-        <v>0.2344020533024273</v>
+        <v>0.2173651276000284</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5080687575091122</v>
+        <v>0.6466414104515442</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-0.1924709191550942</v>
+        <v>0.5053802153887437</v>
       </c>
       <c r="C214" t="n">
-        <v>0.419228712170345</v>
+        <v>0.4885402006963914</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4983254398683405</v>
+        <v>0.6226931387850476</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.3339364551501935</v>
+        <v>0.4077051761387514</v>
       </c>
       <c r="C215" t="n">
-        <v>0.3120264945006955</v>
+        <v>0.02504165818700499</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5097173291140633</v>
+        <v>0.5928777280399471</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -4946,13 +4946,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.3561981120316621</v>
+        <v>-0.3345645625841995</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.2915292807557265</v>
+        <v>-0.1146163157005256</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4954941426118807</v>
+        <v>0.3175980353236082</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -4967,13 +4967,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.1608075198089795</v>
+        <v>-0.3413078079116547</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.2722963097886292</v>
+        <v>0.1886842798462111</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4735403455877102</v>
+        <v>0.3782058738862639</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.3196450972074603</v>
+        <v>0.4545704122382043</v>
       </c>
       <c r="C218" t="n">
-        <v>0.3520120412458081</v>
+        <v>0.04632581499960512</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5228136655400302</v>
+        <v>0.5988000437732565</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5009,13 +5009,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.2226482467716101</v>
+        <v>-0.2662979217864175</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.2178457679068901</v>
+        <v>0.08154109500986383</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4631600688472832</v>
+        <v>0.3552202926993095</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.781546536847583</v>
+        <v>0.06706531959710979</v>
       </c>
       <c r="C220" t="n">
-        <v>0.07082533615554376</v>
+        <v>0.8419937309420793</v>
       </c>
       <c r="D220" t="n">
-        <v>0.6286303937732679</v>
+        <v>0.5021301668078761</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-0.446711138601817</v>
+        <v>-0.440585952710944</v>
       </c>
       <c r="C221" t="n">
-        <v>0.07720918641822709</v>
+        <v>-0.09783950383051443</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2167110844246886</v>
+        <v>0.3528443655207175</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.2628392633448317</v>
+        <v>-0.3765661379312611</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.311373329002173</v>
+        <v>0.02547720568484818</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4721220352015791</v>
+        <v>0.3633065796198204</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.6443678485592947</v>
+        <v>0.04515052942121166</v>
       </c>
       <c r="C223" t="n">
-        <v>0.3368793387166372</v>
+        <v>0.3155818814831148</v>
       </c>
       <c r="D223" t="n">
-        <v>0.6174322948631665</v>
+        <v>0.6124864194170857</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -5114,13 +5114,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.3146810304597119</v>
+        <v>-0.5216991099619368</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.4392078898488707</v>
+        <v>-0.09417681871134481</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4918878385737215</v>
+        <v>0.3555713014613935</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.4362314028925517</v>
+        <v>-0.01394074014631601</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.04576767601407358</v>
+        <v>-0.1720093027473664</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5420456759109358</v>
+        <v>0.3672859143474753</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>-0.2601948611514904</v>
+        <v>-0.8464910790504238</v>
       </c>
       <c r="C226" t="n">
-        <v>0.3017209697004695</v>
+        <v>-0.3469284223791712</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2630135626976943</v>
+        <v>0.1001575263097882</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.291431854150754</v>
+        <v>0.7723770531144505</v>
       </c>
       <c r="C227" t="n">
-        <v>-1.001649270860779</v>
+        <v>-1.157269464434302</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5282972872006944</v>
+        <v>0.5338409869283856</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.2525028201811143</v>
+        <v>-0.1557715971286364</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.1304300127991196</v>
+        <v>0.06398430850570429</v>
       </c>
       <c r="D228" t="n">
-        <v>0.455892895435649</v>
+        <v>0.3075993050556527</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-0.1223534603601002</v>
+        <v>-0.8556989055932304</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1126024280695163</v>
+        <v>-0.0413771897771335</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4115796261237096</v>
+        <v>0.2374151978560419</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -5240,13 +5240,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.3217918672949518</v>
+        <v>0.02303439371494885</v>
       </c>
       <c r="C230" t="n">
-        <v>0.003562449282106554</v>
+        <v>-0.01159313958775005</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4969882498959875</v>
+        <v>0.4091678207011528</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.2505922964784792</v>
+        <v>-0.5557238113735412</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.4713849721375077</v>
+        <v>-0.005565498905251486</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4988690601519287</v>
+        <v>0.3727349820368027</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.216176934908762</v>
+        <v>-0.644529244255444</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.5531267925205738</v>
+        <v>0.1118637309371232</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4744882152611895</v>
+        <v>0.411142017887129</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>-0.5862611536882189</v>
+        <v>-0.7124804324940159</v>
       </c>
       <c r="C233" t="n">
-        <v>0.2985185563922593</v>
+        <v>-0.09865211676749326</v>
       </c>
       <c r="D233" t="n">
-        <v>0.03765064129899173</v>
+        <v>0.3834398401250526</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.5001511817981315</v>
+        <v>1.032835053664523</v>
       </c>
       <c r="C234" t="n">
-        <v>0.8654481340942978</v>
+        <v>-0.2916111397522175</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5406519560059617</v>
+        <v>0.5587473270621742</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.3433550734960776</v>
+        <v>0.1975237341530671</v>
       </c>
       <c r="C235" t="n">
-        <v>0.1364948056226678</v>
+        <v>-0.03657027803879598</v>
       </c>
       <c r="D235" t="n">
-        <v>0.5144801188728054</v>
+        <v>0.5148260375958125</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5366,13 +5366,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.5524013814131469</v>
+        <v>0.622387282415089</v>
       </c>
       <c r="C236" t="n">
-        <v>0.4532271818730187</v>
+        <v>-0.357042029628089</v>
       </c>
       <c r="D236" t="n">
-        <v>0.55575862365632</v>
+        <v>0.5695341156026148</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.2976096153345051</v>
+        <v>-0.4253979908445811</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.3552199619401533</v>
+        <v>-0.03400906303245867</v>
       </c>
       <c r="D237" t="n">
-        <v>0.460157423208647</v>
+        <v>0.3174908295791908</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
